--- a/Assets/Excel/TaskData_4.xlsx
+++ b/Assets/Excel/TaskData_4.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
   <si>
     <t>taskId</t>
   </si>
@@ -133,7 +133,7 @@
     <t>出售青岩剑</t>
   </si>
   <si>
-    <t>提升三号玉砂壶收益</t>
+    <t>提升一号炼器炉收益</t>
   </si>
   <si>
     <t>提升一号灵储阁玄采徒攻击力</t>
@@ -146,9 +146,6 @@
   </si>
   <si>
     <t>解锁巨型铁矿石新区域</t>
-  </si>
-  <si>
-    <t>提升一号炼器炉收益</t>
   </si>
   <si>
     <t>提升二号灵储阁玄采徒攻击力</t>
@@ -827,7 +824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -844,9 +841,6 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1668,7 +1662,7 @@
         <v>7</v>
       </c>
       <c r="F25" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1948,7 +1942,7 @@
         <v>7</v>
       </c>
       <c r="F39" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2136,7 +2130,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1">
         <v>40</v>
@@ -2196,7 +2190,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C52" s="1">
         <v>10</v>
@@ -2236,7 +2230,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C54" s="1">
         <v>50</v>
@@ -2276,7 +2270,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
@@ -2296,7 +2290,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="1">
         <v>1</v>
@@ -2316,7 +2310,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
@@ -2336,7 +2330,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C59" s="1">
         <v>10</v>
@@ -2356,7 +2350,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C60" s="1">
         <v>10</v>
@@ -2376,7 +2370,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="1">
         <v>10</v>
@@ -2396,7 +2390,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C62" s="1">
         <v>10</v>
@@ -2416,7 +2410,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" s="5">
         <v>20</v>
@@ -2476,7 +2470,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C66" s="1">
         <v>60</v>
@@ -2576,7 +2570,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
@@ -2596,7 +2590,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C72" s="1">
         <v>20</v>
@@ -2616,7 +2610,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C73" s="1">
         <v>20</v>
@@ -2636,7 +2630,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C74" s="1">
         <v>20</v>
@@ -2696,7 +2690,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C77" s="1">
         <v>30</v>
@@ -2716,7 +2710,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C78" s="1">
         <v>80</v>
@@ -2776,7 +2770,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C81" s="1">
         <v>30</v>
@@ -2856,7 +2850,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C85" s="1">
         <v>30</v>
@@ -2876,7 +2870,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C86" s="1">
         <v>40</v>
@@ -2896,7 +2890,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
@@ -2916,7 +2910,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
@@ -2936,7 +2930,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C89" s="1">
         <v>1</v>
@@ -2956,7 +2950,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C90" s="1">
         <v>10</v>
@@ -2976,7 +2970,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C91" s="1">
         <v>10</v>
@@ -2996,7 +2990,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C92" s="1">
         <v>10</v>
@@ -3015,8 +3009,8 @@
       <c r="A93" s="1">
         <v>90</v>
       </c>
-      <c r="B93" s="6" t="s">
-        <v>55</v>
+      <c r="B93" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C93" s="1">
         <v>20</v>
@@ -3035,8 +3029,8 @@
       <c r="A94" s="1">
         <v>91</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>47</v>
+      <c r="B94" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C94" s="1">
         <v>50</v>
@@ -3055,7 +3049,7 @@
       <c r="A95" s="1">
         <v>92</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C95" s="1">
@@ -3075,7 +3069,7 @@
       <c r="A96" s="1">
         <v>93</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C96" s="1">
@@ -3095,8 +3089,8 @@
       <c r="A97" s="1">
         <v>94</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>47</v>
+      <c r="B97" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C97" s="1">
         <v>60</v>
@@ -3115,7 +3109,7 @@
       <c r="A98" s="1">
         <v>95</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C98" s="1">
@@ -3135,8 +3129,8 @@
       <c r="A99" s="1">
         <v>96</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>39</v>
+      <c r="B99" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C99" s="1">
         <v>100</v>
@@ -3155,8 +3149,8 @@
       <c r="A100" s="1">
         <v>97</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>40</v>
+      <c r="B100" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C100" s="1">
         <v>40</v>
@@ -3175,8 +3169,8 @@
       <c r="A101" s="1">
         <v>98</v>
       </c>
-      <c r="B101" s="6" t="s">
-        <v>52</v>
+      <c r="B101" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C101" s="1">
         <v>30</v>
@@ -3195,8 +3189,8 @@
       <c r="A102" s="1">
         <v>99</v>
       </c>
-      <c r="B102" s="6" t="s">
-        <v>54</v>
+      <c r="B102" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C102" s="1">
         <v>30</v>
@@ -3215,8 +3209,8 @@
       <c r="A103" s="1">
         <v>100</v>
       </c>
-      <c r="B103" s="6" t="s">
-        <v>56</v>
+      <c r="B103" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C103" s="1">
         <v>800000</v>
